--- a/review-results/河北实时运行及市场出清数据-20260724.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260724.xlsx
@@ -4040,8 +4040,10 @@
       <s:c r="A97" s="9" t="n">
         <s:v>46227</s:v>
       </s:c>
-      <s:c r="B97" s="10" t="n">
-        <s:v>1</s:v>
+      <s:c r="B97" s="10" t="inlineStr">
+        <s:is>
+          <s:t>24:00</s:t>
+        </s:is>
       </s:c>
       <s:c r="C97" s="11" t="n">
         <s:v>24</s:v>
@@ -8980,8 +8982,10 @@
       <s:c r="A97" s="6" t="n">
         <s:v>46227</s:v>
       </s:c>
-      <s:c r="B97" s="7" t="n">
-        <s:v>1</s:v>
+      <s:c r="B97" s="7" t="inlineStr">
+        <s:is>
+          <s:t>24:00</s:t>
+        </s:is>
       </s:c>
       <s:c r="C97" s="1" t="n">
         <s:v>24</s:v>
